--- a/files/iso/DI-IMS-F-01_Rev02.xlsx
+++ b/files/iso/DI-IMS-F-01_Rev02.xlsx
@@ -1438,7 +1438,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr fitToPage="0"/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A2:E32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
@@ -2208,7 +2208,7 @@
     <mergeCell ref="A3:E3"/>
   </mergeCells>
   <pageMargins left="0.7874015748031497" right="0.7874015748031497" top="0.7086614173228347" bottom="0.6299212598425197" header="0.5" footer="0.5"/>
-  <pageSetup orientation="portrait" paperSize="9" scale="100"/>
+  <pageSetup fitToWidth="1" fitToHeight="1" orientation="portrait" paperSize="9" scale="100"/>
   <headerFooter>
     <oddHeader/>
     <oddFooter>&amp;C&amp;"Malgun Gothic"&amp;9 동인엔시스 | DI-IMS-F-01 Rev.02 | 페이지 &amp;P / 전체 &amp;N</oddFooter>
@@ -2225,7 +2225,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr fitToPage="0"/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A2:G20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
@@ -2478,7 +2478,7 @@
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7874015748031497" right="0.7874015748031497" top="0.7086614173228347" bottom="0.6299212598425197" header="0.5" footer="0.5"/>
-  <pageSetup orientation="landscape" paperSize="9" scale="100"/>
+  <pageSetup fitToWidth="1" fitToHeight="1" orientation="landscape" paperSize="9" scale="100"/>
   <headerFooter>
     <oddHeader/>
     <oddFooter>&amp;C&amp;"Malgun Gothic"&amp;9 동인엔시스 | DI-QF-07 Rev.02 | 페이지 &amp;P / 전체 &amp;N</oddFooter>
@@ -2495,7 +2495,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr fitToPage="0"/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A2:G19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
@@ -2687,7 +2687,7 @@
     <mergeCell ref="A5:G5"/>
   </mergeCells>
   <pageMargins left="0.7874015748031497" right="0.7874015748031497" top="0.7086614173228347" bottom="0.6299212598425197" header="0.5" footer="0.5"/>
-  <pageSetup orientation="landscape" paperSize="9" scale="100"/>
+  <pageSetup fitToWidth="1" fitToHeight="1" orientation="landscape" paperSize="9" scale="100"/>
   <headerFooter>
     <oddHeader/>
     <oddFooter>&amp;C&amp;"Malgun Gothic"&amp;9 동인엔시스 | DI-QF-08 Rev.02 | 페이지 &amp;P / 전체 &amp;N</oddFooter>
@@ -2704,7 +2704,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr fitToPage="0"/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A2:G21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
@@ -2952,7 +2952,7 @@
     <mergeCell ref="A5:G5"/>
   </mergeCells>
   <pageMargins left="0.7874015748031497" right="0.7874015748031497" top="0.7086614173228347" bottom="0.6299212598425197" header="0.5" footer="0.5"/>
-  <pageSetup orientation="landscape" paperSize="9" scale="100"/>
+  <pageSetup fitToWidth="1" fitToHeight="1" orientation="landscape" paperSize="9" scale="100"/>
   <headerFooter>
     <oddHeader/>
     <oddFooter>&amp;C&amp;"Malgun Gothic"&amp;9 동인엔시스 | DI-QF-09 Rev.02 | 페이지 &amp;P / 전체 &amp;N</oddFooter>
@@ -2969,7 +2969,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr fitToPage="0"/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A2:G19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
@@ -3161,7 +3161,7 @@
     <mergeCell ref="A5:G5"/>
   </mergeCells>
   <pageMargins left="0.7874015748031497" right="0.7874015748031497" top="0.7086614173228347" bottom="0.6299212598425197" header="0.5" footer="0.5"/>
-  <pageSetup orientation="landscape" paperSize="9" scale="100"/>
+  <pageSetup fitToWidth="1" fitToHeight="1" orientation="landscape" paperSize="9" scale="100"/>
   <headerFooter>
     <oddHeader/>
     <oddFooter>&amp;C&amp;"Malgun Gothic"&amp;9 동인엔시스 | DI-QF-10 Rev.02 | 페이지 &amp;P / 전체 &amp;N</oddFooter>
@@ -3178,7 +3178,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr fitToPage="0"/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A2:G19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
@@ -3370,7 +3370,7 @@
     <mergeCell ref="A5:G5"/>
   </mergeCells>
   <pageMargins left="0.7874015748031497" right="0.7874015748031497" top="0.7086614173228347" bottom="0.6299212598425197" header="0.5" footer="0.5"/>
-  <pageSetup orientation="landscape" paperSize="9" scale="100"/>
+  <pageSetup fitToWidth="1" fitToHeight="1" orientation="landscape" paperSize="9" scale="100"/>
   <headerFooter>
     <oddHeader/>
     <oddFooter>&amp;C&amp;"Malgun Gothic"&amp;9 동인엔시스 | DI-QF-11 Rev.02 | 페이지 &amp;P / 전체 &amp;N</oddFooter>
@@ -3387,7 +3387,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr fitToPage="0"/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A2:G20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
@@ -3587,7 +3587,7 @@
     <mergeCell ref="A5:G5"/>
   </mergeCells>
   <pageMargins left="0.7874015748031497" right="0.7874015748031497" top="0.7086614173228347" bottom="0.6299212598425197" header="0.5" footer="0.5"/>
-  <pageSetup orientation="landscape" paperSize="9" scale="100"/>
+  <pageSetup fitToWidth="1" fitToHeight="1" orientation="landscape" paperSize="9" scale="100"/>
   <headerFooter>
     <oddHeader/>
     <oddFooter>&amp;C&amp;"Malgun Gothic"&amp;9 동인엔시스 | DI-QF-12 Rev.02 | 페이지 &amp;P / 전체 &amp;N</oddFooter>
@@ -3604,7 +3604,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr fitToPage="0"/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A2:G21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
@@ -3812,7 +3812,7 @@
     <mergeCell ref="A5:G5"/>
   </mergeCells>
   <pageMargins left="0.7874015748031497" right="0.7874015748031497" top="0.7086614173228347" bottom="0.6299212598425197" header="0.5" footer="0.5"/>
-  <pageSetup orientation="landscape" paperSize="9" scale="100"/>
+  <pageSetup fitToWidth="1" fitToHeight="1" orientation="landscape" paperSize="9" scale="100"/>
   <headerFooter>
     <oddHeader/>
     <oddFooter>&amp;C&amp;"Malgun Gothic"&amp;9 동인엔시스 | DI-QF-13 Rev.02 | 페이지 &amp;P / 전체 &amp;N</oddFooter>
@@ -3829,7 +3829,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr fitToPage="0"/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A2:G18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
@@ -4013,7 +4013,7 @@
     <mergeCell ref="A5:G5"/>
   </mergeCells>
   <pageMargins left="0.7874015748031497" right="0.7874015748031497" top="0.7086614173228347" bottom="0.6299212598425197" header="0.5" footer="0.5"/>
-  <pageSetup orientation="landscape" paperSize="9" scale="100"/>
+  <pageSetup fitToWidth="1" fitToHeight="1" orientation="landscape" paperSize="9" scale="100"/>
   <headerFooter>
     <oddHeader/>
     <oddFooter>&amp;C&amp;"Malgun Gothic"&amp;9 동인엔시스 | DI-QF-14 Rev.02 | 페이지 &amp;P / 전체 &amp;N</oddFooter>
@@ -4030,7 +4030,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr fitToPage="0"/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A2:G24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
@@ -4362,7 +4362,7 @@
     <mergeCell ref="A23:G23"/>
   </mergeCells>
   <pageMargins left="0.7874015748031497" right="0.7874015748031497" top="0.7086614173228347" bottom="0.6299212598425197" header="0.5" footer="0.5"/>
-  <pageSetup orientation="landscape" paperSize="9" scale="100"/>
+  <pageSetup fitToWidth="1" fitToHeight="1" orientation="landscape" paperSize="9" scale="100"/>
   <headerFooter>
     <oddHeader/>
     <oddFooter>&amp;C&amp;"Malgun Gothic"&amp;9 동인엔시스 | DI-QF-15 Rev.02 | 페이지 &amp;P / 전체 &amp;N</oddFooter>
@@ -4379,7 +4379,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr fitToPage="0"/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A2:H19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
@@ -4609,7 +4609,7 @@
     <mergeCell ref="A6:H6"/>
   </mergeCells>
   <pageMargins left="0.7874015748031497" right="0.7874015748031497" top="0.7086614173228347" bottom="0.6299212598425197" header="0.5" footer="0.5"/>
-  <pageSetup orientation="landscape" paperSize="9" scale="100"/>
+  <pageSetup fitToWidth="1" fitToHeight="1" orientation="landscape" paperSize="9" scale="100"/>
   <headerFooter>
     <oddHeader/>
     <oddFooter>&amp;C&amp;"Malgun Gothic"&amp;9 동인엔시스 | DI-QF-16 Rev.02 | 페이지 &amp;P / 전체 &amp;N</oddFooter>
@@ -4626,7 +4626,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr fitToPage="0"/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A2:E12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
@@ -4759,7 +4759,7 @@
     <mergeCell ref="A3:E3"/>
   </mergeCells>
   <pageMargins left="0.7874015748031497" right="0.7874015748031497" top="0.7086614173228347" bottom="0.6299212598425197" header="0.5" footer="0.5"/>
-  <pageSetup orientation="portrait" paperSize="9" scale="100"/>
+  <pageSetup fitToWidth="1" fitToHeight="1" orientation="portrait" paperSize="9" scale="100"/>
   <headerFooter>
     <oddHeader/>
     <oddFooter>&amp;C&amp;"Malgun Gothic"&amp;9 동인엔시스 | DI-IMS-F-01 Rev.02 | 페이지 &amp;P / 전체 &amp;N</oddFooter>
@@ -4776,7 +4776,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr fitToPage="0"/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A2:H21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
@@ -5052,7 +5052,7 @@
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7874015748031497" right="0.7874015748031497" top="0.7086614173228347" bottom="0.6299212598425197" header="0.5" footer="0.5"/>
-  <pageSetup orientation="landscape" paperSize="9" scale="100"/>
+  <pageSetup fitToWidth="1" fitToHeight="1" orientation="landscape" paperSize="9" scale="100"/>
   <headerFooter>
     <oddHeader/>
     <oddFooter>&amp;C&amp;"Malgun Gothic"&amp;9 동인엔시스 | DI-SF-01 Rev.02 | 페이지 &amp;P / 전체 &amp;N</oddFooter>
@@ -5069,7 +5069,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr fitToPage="0"/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A2:E21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
@@ -5297,7 +5297,7 @@
     <mergeCell ref="A3:E3"/>
   </mergeCells>
   <pageMargins left="0.7874015748031497" right="0.7874015748031497" top="0.7086614173228347" bottom="0.6299212598425197" header="0.5" footer="0.5"/>
-  <pageSetup orientation="portrait" paperSize="9" scale="100"/>
+  <pageSetup fitToWidth="1" fitToHeight="1" orientation="portrait" paperSize="9" scale="100"/>
   <headerFooter>
     <oddHeader/>
     <oddFooter>&amp;C&amp;"Malgun Gothic"&amp;9 동인엔시스 | DI-SF-02 Rev.02 | 페이지 &amp;P / 전체 &amp;N</oddFooter>
@@ -5314,7 +5314,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr fitToPage="0"/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A2:F20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
@@ -5540,7 +5540,7 @@
     <mergeCell ref="A7:F7"/>
   </mergeCells>
   <pageMargins left="0.7874015748031497" right="0.7874015748031497" top="0.7086614173228347" bottom="0.6299212598425197" header="0.5" footer="0.5"/>
-  <pageSetup orientation="landscape" paperSize="9" scale="100"/>
+  <pageSetup fitToWidth="1" fitToHeight="1" orientation="landscape" paperSize="9" scale="100"/>
   <headerFooter>
     <oddHeader/>
     <oddFooter>&amp;C&amp;"Malgun Gothic"&amp;9 동인엔시스 | DI-SF-03 Rev.02 | 페이지 &amp;P / 전체 &amp;N</oddFooter>
@@ -5557,7 +5557,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr fitToPage="0"/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A2:H21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
@@ -5861,7 +5861,7 @@
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7874015748031497" right="0.7874015748031497" top="0.7086614173228347" bottom="0.6299212598425197" header="0.5" footer="0.5"/>
-  <pageSetup orientation="landscape" paperSize="9" scale="100"/>
+  <pageSetup fitToWidth="1" fitToHeight="1" orientation="landscape" paperSize="9" scale="100"/>
   <headerFooter>
     <oddHeader/>
     <oddFooter>&amp;C&amp;"Malgun Gothic"&amp;9 동인엔시스 | DI-EF-01 Rev.02 | 페이지 &amp;P / 전체 &amp;N</oddFooter>
@@ -5878,7 +5878,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr fitToPage="0"/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A2:G21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
@@ -6164,7 +6164,7 @@
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7874015748031497" right="0.7874015748031497" top="0.7086614173228347" bottom="0.6299212598425197" header="0.5" footer="0.5"/>
-  <pageSetup orientation="landscape" paperSize="9" scale="100"/>
+  <pageSetup fitToWidth="1" fitToHeight="1" orientation="landscape" paperSize="9" scale="100"/>
   <headerFooter>
     <oddHeader/>
     <oddFooter>&amp;C&amp;"Malgun Gothic"&amp;9 동인엔시스 | DI-MF-01 Rev.02 | 페이지 &amp;P / 전체 &amp;N</oddFooter>
@@ -6181,7 +6181,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr fitToPage="0"/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A2:F20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
@@ -6439,7 +6439,7 @@
     <mergeCell ref="A7:F7"/>
   </mergeCells>
   <pageMargins left="0.7874015748031497" right="0.7874015748031497" top="0.7086614173228347" bottom="0.6299212598425197" header="0.5" footer="0.5"/>
-  <pageSetup orientation="landscape" paperSize="9" scale="100"/>
+  <pageSetup fitToWidth="1" fitToHeight="1" orientation="landscape" paperSize="9" scale="100"/>
   <headerFooter>
     <oddHeader/>
     <oddFooter>&amp;C&amp;"Malgun Gothic"&amp;9 동인엔시스 | DI-MF-02 Rev.02 | 페이지 &amp;P / 전체 &amp;N</oddFooter>
@@ -6456,7 +6456,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr fitToPage="0"/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A2:G19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
@@ -6664,7 +6664,7 @@
     <mergeCell ref="A5:G5"/>
   </mergeCells>
   <pageMargins left="0.7874015748031497" right="0.7874015748031497" top="0.7086614173228347" bottom="0.6299212598425197" header="0.5" footer="0.5"/>
-  <pageSetup orientation="landscape" paperSize="9" scale="100"/>
+  <pageSetup fitToWidth="1" fitToHeight="1" orientation="landscape" paperSize="9" scale="100"/>
   <headerFooter>
     <oddHeader/>
     <oddFooter>&amp;C&amp;"Malgun Gothic"&amp;9 동인엔시스 | DI-MF-03 Rev.02 | 페이지 &amp;P / 전체 &amp;N</oddFooter>
@@ -6681,7 +6681,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr fitToPage="0"/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A2:G19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
@@ -6921,7 +6921,7 @@
     <mergeCell ref="A5:G5"/>
   </mergeCells>
   <pageMargins left="0.7874015748031497" right="0.7874015748031497" top="0.7086614173228347" bottom="0.6299212598425197" header="0.5" footer="0.5"/>
-  <pageSetup orientation="landscape" paperSize="9" scale="100"/>
+  <pageSetup fitToWidth="1" fitToHeight="1" orientation="landscape" paperSize="9" scale="100"/>
   <headerFooter>
     <oddHeader/>
     <oddFooter>&amp;C&amp;"Malgun Gothic"&amp;9 동인엔시스 | DI-MF-04 Rev.02 | 페이지 &amp;P / 전체 &amp;N</oddFooter>
@@ -6938,7 +6938,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr fitToPage="0"/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A2:H20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
@@ -7213,7 +7213,7 @@
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7874015748031497" right="0.7874015748031497" top="0.7086614173228347" bottom="0.6299212598425197" header="0.5" footer="0.5"/>
-  <pageSetup orientation="landscape" paperSize="9" scale="100"/>
+  <pageSetup fitToWidth="1" fitToHeight="1" orientation="landscape" paperSize="9" scale="100"/>
   <headerFooter>
     <oddHeader/>
     <oddFooter>&amp;C&amp;"Malgun Gothic"&amp;9 동인엔시스 | DI-MF-05 Rev.02 | 페이지 &amp;P / 전체 &amp;N</oddFooter>
@@ -7230,7 +7230,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr fitToPage="0"/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A2:F22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
@@ -7432,7 +7432,7 @@
     <mergeCell ref="A7:F7"/>
   </mergeCells>
   <pageMargins left="0.7874015748031497" right="0.7874015748031497" top="0.7086614173228347" bottom="0.6299212598425197" header="0.5" footer="0.5"/>
-  <pageSetup orientation="landscape" paperSize="9" scale="100"/>
+  <pageSetup fitToWidth="1" fitToHeight="1" orientation="landscape" paperSize="9" scale="100"/>
   <headerFooter>
     <oddHeader/>
     <oddFooter>&amp;C&amp;"Malgun Gothic"&amp;9 동인엔시스 | DI-MF-06 Rev.02 | 페이지 &amp;P / 전체 &amp;N</oddFooter>
@@ -7449,7 +7449,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr fitToPage="0"/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A2:E10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
@@ -7530,7 +7530,7 @@
     <mergeCell ref="A3:E3"/>
   </mergeCells>
   <pageMargins left="0.7874015748031497" right="0.7874015748031497" top="0.7086614173228347" bottom="0.6299212598425197" header="0.5" footer="0.5"/>
-  <pageSetup orientation="portrait" paperSize="9" scale="100"/>
+  <pageSetup fitToWidth="1" fitToHeight="1" orientation="portrait" paperSize="9" scale="100"/>
   <headerFooter>
     <oddHeader/>
     <oddFooter>&amp;C&amp;"Malgun Gothic"&amp;9 동인엔시스 | DI-IMS-F-01 Rev.02 | 페이지 &amp;P / 전체 &amp;N</oddFooter>
@@ -7547,7 +7547,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr fitToPage="0"/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A2:F22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
@@ -7805,7 +7805,7 @@
     <mergeCell ref="A7:F7"/>
   </mergeCells>
   <pageMargins left="0.7874015748031497" right="0.7874015748031497" top="0.7086614173228347" bottom="0.6299212598425197" header="0.5" footer="0.5"/>
-  <pageSetup orientation="landscape" paperSize="9" scale="100"/>
+  <pageSetup fitToWidth="1" fitToHeight="1" orientation="landscape" paperSize="9" scale="100"/>
   <headerFooter>
     <oddHeader/>
     <oddFooter>&amp;C&amp;"Malgun Gothic"&amp;9 동인엔시스 | DI-PF-00 Rev.02 | 페이지 &amp;P / 전체 &amp;N</oddFooter>
@@ -7822,7 +7822,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr fitToPage="0"/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A2:G20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
@@ -8062,7 +8062,7 @@
     <mergeCell ref="A5:G5"/>
   </mergeCells>
   <pageMargins left="0.7874015748031497" right="0.7874015748031497" top="0.7086614173228347" bottom="0.6299212598425197" header="0.5" footer="0.5"/>
-  <pageSetup orientation="landscape" paperSize="9" scale="100"/>
+  <pageSetup fitToWidth="1" fitToHeight="1" orientation="landscape" paperSize="9" scale="100"/>
   <headerFooter>
     <oddHeader/>
     <oddFooter>&amp;C&amp;"Malgun Gothic"&amp;9 동인엔시스 | DI-QF-02 Rev.02 | 페이지 &amp;P / 전체 &amp;N</oddFooter>
@@ -8079,7 +8079,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr fitToPage="0"/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A2:G19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
@@ -8276,7 +8276,7 @@
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7874015748031497" right="0.7874015748031497" top="0.7086614173228347" bottom="0.6299212598425197" header="0.5" footer="0.5"/>
-  <pageSetup orientation="landscape" paperSize="9" scale="100"/>
+  <pageSetup fitToWidth="1" fitToHeight="1" orientation="landscape" paperSize="9" scale="100"/>
   <headerFooter>
     <oddHeader/>
     <oddFooter>&amp;C&amp;"Malgun Gothic"&amp;9 동인엔시스 | DI-QF-03 Rev.02 | 페이지 &amp;P / 전체 &amp;N</oddFooter>
@@ -8293,7 +8293,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr fitToPage="0"/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A2:G18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
@@ -8477,7 +8477,7 @@
     <mergeCell ref="A5:G5"/>
   </mergeCells>
   <pageMargins left="0.7874015748031497" right="0.7874015748031497" top="0.7086614173228347" bottom="0.6299212598425197" header="0.5" footer="0.5"/>
-  <pageSetup orientation="landscape" paperSize="9" scale="100"/>
+  <pageSetup fitToWidth="1" fitToHeight="1" orientation="landscape" paperSize="9" scale="100"/>
   <headerFooter>
     <oddHeader/>
     <oddFooter>&amp;C&amp;"Malgun Gothic"&amp;9 동인엔시스 | DI-QF-04 Rev.02 | 페이지 &amp;P / 전체 &amp;N</oddFooter>
@@ -8494,7 +8494,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr fitToPage="0"/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A2:F19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
@@ -8744,7 +8744,7 @@
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7874015748031497" right="0.7874015748031497" top="0.7086614173228347" bottom="0.6299212598425197" header="0.5" footer="0.5"/>
-  <pageSetup orientation="landscape" paperSize="9" scale="100"/>
+  <pageSetup fitToWidth="1" fitToHeight="1" orientation="landscape" paperSize="9" scale="100"/>
   <headerFooter>
     <oddHeader/>
     <oddFooter>&amp;C&amp;"Malgun Gothic"&amp;9 동인엔시스 | DI-QF-05 Rev.02 | 페이지 &amp;P / 전체 &amp;N</oddFooter>
@@ -8761,7 +8761,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr fitToPage="0"/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A2:G21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
@@ -9047,7 +9047,7 @@
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7874015748031497" right="0.7874015748031497" top="0.7086614173228347" bottom="0.6299212598425197" header="0.5" footer="0.5"/>
-  <pageSetup orientation="landscape" paperSize="9" scale="100"/>
+  <pageSetup fitToWidth="1" fitToHeight="1" orientation="landscape" paperSize="9" scale="100"/>
   <headerFooter>
     <oddHeader/>
     <oddFooter>&amp;C&amp;"Malgun Gothic"&amp;9 동인엔시스 | DI-QF-06 Rev.02 | 페이지 &amp;P / 전체 &amp;N</oddFooter>
